--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_392_R43.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_392_R43.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.4938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9624</v>
+        <v>0.4506</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0214</v>
+        <v>0.0432</v>
       </c>
       <c r="G2" t="n">
         <v>-1.1853</v>
@@ -610,13 +610,13 @@
         <v>1.3648</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7615</v>
+        <v>0.3143</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6227</v>
+        <v>0.1109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1388</v>
+        <v>0.2034</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6032999999999999</v>
+        <v>0.0127</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6973</v>
+        <v>2.1193</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3005</v>
+        <v>-2.1066</v>
       </c>
       <c r="G3" t="n">
         <v>0.4767</v>
@@ -688,13 +688,13 @@
         <v>1.8198</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7623</v>
+        <v>-1.1464</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3647</v>
+        <v>-0.9427</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3976</v>
+        <v>-0.2037</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.9424</v>
+        <v>-1.0481</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7102</v>
+        <v>2.249</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.6526</v>
+        <v>-3.2971</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1517</v>
@@ -766,13 +766,13 @@
         <v>1.5923</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5588</v>
+        <v>-0.6645</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.221</v>
+        <v>-0.6823</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3377</v>
+        <v>0.0178</v>
       </c>
       <c r="V4" t="n">
         <v>2.7253</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2624</v>
+        <v>-2.4168</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4733</v>
+        <v>-0.4015</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7891</v>
+        <v>-2.0153</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3007</v>
@@ -844,13 +844,13 @@
         <v>2.5022</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.9997</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0892</v>
+        <v>-1.0174</v>
       </c>
       <c r="U5" t="n">
-        <v>0.244</v>
+        <v>0.0177</v>
       </c>
       <c r="V5" t="n">
         <v>1.7935</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.4254</v>
+        <v>-2.6265</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2333</v>
+        <v>-1.4667</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1921</v>
+        <v>-1.1598</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3728</v>
@@ -922,13 +922,13 @@
         <v>1.5923</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4812</v>
+        <v>-0.6824</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4428</v>
+        <v>-0.6763</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0384</v>
+        <v>-0.0061</v>
       </c>
       <c r="V6" t="n">
         <v>1.2485</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.9794</v>
+        <v>-7.3601</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6986</v>
+        <v>-2.6268</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.2808</v>
+        <v>-4.7333</v>
       </c>
       <c r="G7" t="n">
         <v>-4.7546</v>
@@ -1000,13 +1000,13 @@
         <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2729</v>
+        <v>-0.1077</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4428</v>
+        <v>-0.371</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7157</v>
+        <v>0.2632</v>
       </c>
       <c r="V7" t="n">
         <v>-2.7253</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.3138</v>
+        <v>-7.4952</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9331</v>
+        <v>-2.0498</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.3807</v>
+        <v>-5.4454</v>
       </c>
       <c r="G8" t="n">
         <v>-5.8454</v>
@@ -1078,13 +1078,13 @@
         <v>1.5923</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.0146</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7301</v>
+        <v>-0.8468</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1031</v>
+        <v>-0.1677</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0901</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.0434</v>
+        <v>-7.8297</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9168</v>
+        <v>-2.8001</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.1266</v>
+        <v>-5.0297</v>
       </c>
       <c r="G9" t="n">
         <v>-4.88</v>
@@ -1156,13 +1156,13 @@
         <v>0.6824</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1206</v>
+        <v>-0.9069</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7183</v>
+        <v>-0.6015</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4023</v>
+        <v>-0.3053</v>
       </c>
       <c r="V9" t="n">
         <v>-2.7253</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-28.6291</v>
+        <v>-28.2699</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.885200000000001</v>
+        <v>-4.526</v>
       </c>
       <c r="F10" t="n">
-        <v>-23.7438</v>
+        <v>-23.744</v>
       </c>
       <c r="G10" t="n">
         <v>-20.0138</v>
@@ -1234,13 +1234,13 @@
         <v>12.5109</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.567</v>
+        <v>-5.2079</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.386200000000001</v>
+        <v>-5.0271</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1806</v>
+        <v>-0.1807</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7733999999999996</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.0735</v>
+        <v>7.7667</v>
       </c>
       <c r="E11" t="n">
-        <v>4.844</v>
+        <v>5.311</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2294</v>
+        <v>2.4557</v>
       </c>
       <c r="G11" t="n">
         <v>5.0783</v>
@@ -1312,13 +1312,13 @@
         <v>2.0473</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2227</v>
+        <v>0.9159</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2513</v>
+        <v>0.2156</v>
       </c>
       <c r="U11" t="n">
-        <v>0.474</v>
+        <v>0.7002</v>
       </c>
       <c r="V11" t="n">
         <v>1.0901</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2795</v>
+        <v>5.4571</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9303</v>
+        <v>4.4633</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3493</v>
+        <v>0.9937</v>
       </c>
       <c r="G12" t="n">
         <v>4.3638</v>
@@ -1390,13 +1390,13 @@
         <v>0.9099</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2115</v>
+        <v>0.389</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2755</v>
+        <v>-0.1915</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.5805</v>
       </c>
       <c r="V12" t="n">
         <v>0.9318</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.45</v>
+        <v>4.8451</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7383</v>
+        <v>3.9718</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7117</v>
+        <v>0.8733</v>
       </c>
       <c r="G13" t="n">
         <v>6.1022</v>
@@ -1468,13 +1468,13 @@
         <v>2.2747</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5148</v>
+        <v>-0.1198</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6344</v>
+        <v>-0.401</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1196</v>
+        <v>0.2812</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6238</v>
+        <v>4.2452</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2593</v>
+        <v>4.4928</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6355</v>
+        <v>-0.2476</v>
       </c>
       <c r="G14" t="n">
         <v>3.1793</v>
@@ -1546,13 +1546,13 @@
         <v>0.9099</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0105</v>
+        <v>-0.3891</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7183</v>
+        <v>-0.4848</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2922</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.5451</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4703</v>
+        <v>3.3661</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7373</v>
+        <v>2.5038</v>
       </c>
       <c r="F15" t="n">
-        <v>0.733</v>
+        <v>0.8623</v>
       </c>
       <c r="G15" t="n">
         <v>0.8339</v>
@@ -1624,13 +1624,13 @@
         <v>2.0473</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8166</v>
+        <v>0.7124</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4551</v>
+        <v>0.2216</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3615</v>
+        <v>0.4908</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2993</v>
+        <v>2.7229</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6239</v>
+        <v>2.2737</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6755</v>
+        <v>0.4492</v>
       </c>
       <c r="G16" t="n">
         <v>2.8559</v>
@@ -1702,13 +1702,13 @@
         <v>0.9099</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0104</v>
+        <v>0.4339</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3473</v>
+        <v>-0.0029</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6631</v>
+        <v>0.4368</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4768</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5269</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0508</v>
+        <v>1.437</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5239</v>
+        <v>0.233</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0693</v>
+        <v>0.4309</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8439</v>
+        <v>0.6038</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9132</v>
+        <v>-0.173</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7451</v>
+        <v>1.4609</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4313</v>
+        <v>0.8608</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3137</v>
+        <v>0.6001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6758</v>
+        <v>-1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2752</v>
+        <v>-0.2569</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4006</v>
+        <v>-0.7731</v>
       </c>
       <c r="P17" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.2275</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.6824</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-1.3648</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.0473</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.4104</v>
+        <v>0.7842</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6706</v>
+        <v>0.2036</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7398</v>
+        <v>0.5806</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6352</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3635</v>
+        <v>1.4425</v>
       </c>
       <c r="E18" t="n">
-        <v>1.048</v>
+        <v>1.934</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3155</v>
+        <v>-0.4915</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.271</v>
+        <v>1.0693</v>
       </c>
       <c r="H18" t="n">
-        <v>0.051</v>
+        <v>-0.8439</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.322</v>
+        <v>1.9132</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1316</v>
+        <v>2.7451</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2434</v>
+        <v>0.4313</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1118</v>
+        <v>2.3137</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1393</v>
+        <v>-1.6758</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2944</v>
+        <v>-1.2752</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4338</v>
+        <v>-0.4006</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6824</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.3648</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.0473</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0895</v>
+        <v>1.326</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.5538</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4549</v>
+        <v>0.7721</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5451</v>
+        <v>-1.6352</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9768</v>
+        <v>0.735</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9701</v>
+        <v>0.581</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0067</v>
+        <v>0.1539</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4309</v>
+        <v>-0.271</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6038</v>
+        <v>0.051</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.173</v>
+        <v>-0.322</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4609</v>
+        <v>-0.1316</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8608</v>
+        <v>-0.2434</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6001</v>
+        <v>0.1118</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.03</v>
+        <v>-0.1393</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2569</v>
+        <v>0.2944</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7731</v>
+        <v>-0.4338</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4549</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2275</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6824</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.091</v>
+        <v>0.4609</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2633</v>
+        <v>0.1676</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3543</v>
+        <v>0.2933</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>M. MORRIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9893999999999999</v>
+        <v>0.1167</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2908</v>
+        <v>0.1167</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3014</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1328</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1031</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.236</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7022</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6882</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.014</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5694</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7914</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3648</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9099</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4407</v>
+        <v>0.1167</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7183</v>
+        <v>0.1167</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2776</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3167</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4452</v>
+        <v>-0.9049</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8024</v>
+        <v>-1.1741</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3572</v>
+        <v>0.2691</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.7612</v>
+        <v>1.1328</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7999</v>
+        <v>-0.1031</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9614</v>
+        <v>1.236</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7736</v>
+        <v>1.7022</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3353</v>
+        <v>0.6882</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.4383</v>
+        <v>1.014</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9876</v>
+        <v>-0.5694</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4646</v>
+        <v>-0.7914</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.523</v>
+        <v>0.222</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4549</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5022</v>
+        <v>-2.2747</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0473</v>
+        <v>0.9099</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6809</v>
+        <v>-0.3562</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3833</v>
+        <v>-0.6015</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2976</v>
+        <v>0.2453</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0901</v>
+        <v>-0.3167</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,66 +2125,144 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>28.629</v>
+        <v>-2.8331</v>
       </c>
       <c r="E22" t="n">
-        <v>22.1088</v>
+        <v>-3.8024</v>
       </c>
       <c r="F22" t="n">
-        <v>6.520300000000001</v>
+        <v>0.9694</v>
       </c>
       <c r="G22" t="n">
+        <v>-4.7612</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.7999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2.9614</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2.7736</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.3353</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2.4383</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.9876</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.4646</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.523</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.4549</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.5022</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.0473</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.9098000000000001</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.0901</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.0901</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OLYMPIACOS PIRAEUS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.6293</v>
+      </c>
+      <c r="E23" t="n">
+        <v>22.1086</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.5205</v>
+      </c>
+      <c r="G23" t="n">
         <v>20.0142</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>-3.2817</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>23.2959</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>28.127</v>
       </c>
-      <c r="K22" t="n">
-        <v>6.2728</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K23" t="n">
+        <v>6.272799999999999</v>
+      </c>
+      <c r="L23" t="n">
         <v>21.8539</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>-8.1126</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-9.5547</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>1.4419</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>2.274700000000001</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>-12.511</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>14.7859</v>
       </c>
-      <c r="S22" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.1808000000000001</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5.3862</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.7735000000000003</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="S23" t="n">
+        <v>5.5669</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1804999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5.3863</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.7735000000000002</v>
+      </c>
+      <c r="W23" t="n">
         <v>6.3123</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>-5.5389</v>
       </c>
     </row>
